--- a/Employee_Reports_wi52/Nhuel Caguicla Landicho Q0329.xlsx
+++ b/Employee_Reports_wi52/Nhuel Caguicla Landicho Q0329.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-252</v>
+        <v>-260</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-163</v>
+        <v>-171</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-148</v>
+        <v>-156</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -860,11 +860,11 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
